--- a/Docs/Para Compartir IA/Analisis Origen Destino Campos Inventario.xlsx
+++ b/Docs/Para Compartir IA/Analisis Origen Destino Campos Inventario.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Desarrollos\MyPython\Tkinter\ArkConInv\Docs\Para Compartir IA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{77351579-EE27-43FE-9AC9-0A76EA9A7023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52795590-CA1A-4BD7-AF3E-33E418EBC62D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Analisis Origen Destino Campos " sheetId="2" r:id="rId2"/>
+    <sheet name="Origen Destino Campos New" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="195">
   <si>
     <t>Source Column Name</t>
   </si>
@@ -641,12 +642,100 @@
   <si>
     <t>system_info.get_current_user()</t>
   </si>
+  <si>
+    <t>inv_uo_id</t>
+  </si>
+  <si>
+    <t>inv_dep_IDauto</t>
+  </si>
+  <si>
+    <t>ark_unds_operativas.uo_id</t>
+  </si>
+  <si>
+    <t>ark_depositos.dep_Idauto</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>system_info</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.get_date_audit()</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>system_info</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.get_time_audit()</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>system_info</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.get_machine_name()</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>system_info</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.get_current_user()</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -665,6 +754,17 @@
     <font>
       <sz val="11"/>
       <color rgb="FFD4D4D4"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
@@ -689,12 +789,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3514,4 +3615,944 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FEDF598-7E81-4099-9BA3-63717999B2BB}">
+  <dimension ref="A1:C84"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C5" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C6" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C21" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C23" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C24" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C25" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C26" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C27" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C28" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C29" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C30" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C31" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C32" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C33" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C34" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C35" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C36" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C37" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C38" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C39" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C40" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C41" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C42" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C43" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C44" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C45" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C46" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C47" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C48" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C49" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C50" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C51" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C52" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C53" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C54" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C55" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C56" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C57" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C58" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C59" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C60" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C61" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C62" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C63" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C64" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C65" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C66" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C67" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C68" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C69" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C70" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C71" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C72" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C73" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C74" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C75" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C76" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C81" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C82" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C83" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C84" t="s">
+        <v>186</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>